--- a/output/项目成果分析.xlsx
+++ b/output/项目成果分析.xlsx
@@ -14,6 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="定价建议" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="价格带明细" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="清洗后明细" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AB实验设计" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AB测试结果" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AB分组汇总" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,6 +672,92 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>visits</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gmv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>140829</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11314</v>
+      </c>
+      <c r="D2" t="n">
+        <v>656212</v>
+      </c>
+      <c r="E2" t="n">
+        <v>407304</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>139469</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15254</v>
+      </c>
+      <c r="D3" t="n">
+        <v>594906</v>
+      </c>
+      <c r="E3" t="n">
+        <v>259318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1813,7 +1902,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -1880,7 +1969,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -1947,7 +2036,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -2014,7 +2103,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -2081,7 +2170,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -2148,7 +2237,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -2215,7 +2304,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2282,7 +2371,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2349,7 +2438,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2416,7 +2505,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2483,7 +2572,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2550,7 +2639,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2617,7 +2706,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2684,7 +2773,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2751,7 +2840,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2818,7 +2907,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2885,7 +2974,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -2952,7 +3041,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3019,7 +3108,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3086,7 +3175,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3153,7 +3242,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3220,7 +3309,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3287,7 +3376,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -3354,7 +3443,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -3421,7 +3510,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -3488,7 +3577,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -3555,7 +3644,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -3622,7 +3711,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -3689,7 +3778,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -3756,7 +3845,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -3823,7 +3912,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -3890,7 +3979,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -3957,7 +4046,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -4024,7 +4113,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -4091,7 +4180,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -4158,7 +4247,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -4225,7 +4314,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -4292,7 +4381,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -4359,7 +4448,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -4426,7 +4515,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -4493,7 +4582,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -4560,7 +4649,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -4627,7 +4716,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -4694,7 +4783,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -4761,7 +4850,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -4828,7 +4917,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -4895,7 +4984,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -4962,7 +5051,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -5029,7 +5118,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -5096,7 +5185,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -5163,7 +5252,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -5230,7 +5319,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -5297,7 +5386,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -5364,7 +5453,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -5431,7 +5520,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -5498,7 +5587,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -5565,7 +5654,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -5632,7 +5721,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -5699,7 +5788,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -5766,7 +5855,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -5833,7 +5922,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -5900,7 +5989,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -5967,7 +6056,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -6034,7 +6123,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -6101,7 +6190,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -6168,7 +6257,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -6235,7 +6324,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -6302,7 +6391,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -6369,7 +6458,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -6436,7 +6525,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -6503,7 +6592,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -6570,7 +6659,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -6637,7 +6726,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -6704,7 +6793,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -6771,7 +6860,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -6838,7 +6927,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -6905,7 +6994,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -6972,7 +7061,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -7039,7 +7128,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -7106,7 +7195,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -7173,7 +7262,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -7240,7 +7329,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -7307,7 +7396,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -7374,7 +7463,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -7441,7 +7530,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -7508,7 +7597,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -7575,7 +7664,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -7642,7 +7731,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-08-19T22:16:38</t>
+          <t>2026-08-19T22:51:32</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -7652,6 +7741,277 @@
         <is>
           <t>100-119</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>control_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>treatment_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unit_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sample_size_per_group</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>duration_days</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>daily_traffic_per_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>control_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>treatment_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>lift_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>两样本比例 z 检验</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>日订单量</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Welch t 检验</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>808.14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1089.57</v>
+      </c>
+      <c r="E3" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>日GMV</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Welch t 检验</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>46872.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42493.29</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-9.34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>日毛利</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Welch t 检验</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>29093.14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18522.71</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-36.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/项目成果分析.xlsx
+++ b/output/项目成果分析.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -495,26 +495,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G2" t="n">
-        <v>1669.8</v>
+        <v>1348.9</v>
       </c>
       <c r="H2" t="n">
-        <v>25047</v>
+        <v>20234</v>
       </c>
     </row>
     <row r="3">
@@ -525,26 +525,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>抖音</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>34.5</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
-        <v>5480.6</v>
+        <v>1274.9</v>
       </c>
       <c r="H3" t="n">
-        <v>76729</v>
+        <v>19124</v>
       </c>
     </row>
     <row r="4">
@@ -555,56 +555,56 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>513.5</v>
+        <v>3010.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7702</v>
+        <v>39136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G5" t="n">
-        <v>1935.4</v>
+        <v>513.5</v>
       </c>
       <c r="H5" t="n">
-        <v>29031</v>
+        <v>7702</v>
       </c>
     </row>
     <row r="6">
@@ -615,26 +615,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="G6" t="n">
-        <v>5997.8</v>
+        <v>822</v>
       </c>
       <c r="H6" t="n">
-        <v>89967</v>
+        <v>11508</v>
       </c>
     </row>
     <row r="7">
@@ -645,26 +645,86 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>49</v>
+      </c>
+      <c r="E7" t="n">
+        <v>84</v>
+      </c>
+      <c r="F7" t="n">
+        <v>133</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2480.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>37204</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>拼多多</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" t="n">
+        <v>68</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7880.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>110324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>淘宝</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" t="n">
         <v>14</v>
       </c>
-      <c r="D7" t="n">
-        <v>59</v>
-      </c>
-      <c r="E7" t="n">
-        <v>118</v>
-      </c>
-      <c r="F7" t="n">
-        <v>166</v>
-      </c>
-      <c r="G7" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6141</v>
+      <c r="D9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>179</v>
+      </c>
+      <c r="G9" t="n">
+        <v>503.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7044</v>
       </c>
     </row>
   </sheetData>
@@ -728,10 +788,10 @@
         <v>11314</v>
       </c>
       <c r="D2" t="n">
-        <v>656212</v>
+        <v>837236</v>
       </c>
       <c r="E2" t="n">
-        <v>407304</v>
+        <v>588328</v>
       </c>
     </row>
     <row r="3">
@@ -747,10 +807,10 @@
         <v>15254</v>
       </c>
       <c r="D3" t="n">
-        <v>594906</v>
+        <v>747446</v>
       </c>
       <c r="E3" t="n">
-        <v>259318</v>
+        <v>411858</v>
       </c>
     </row>
   </sheetData>
@@ -813,13 +873,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1073</v>
+        <v>3526</v>
       </c>
       <c r="E2" t="n">
-        <v>536.5</v>
+        <v>587.6666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -834,13 +894,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>246</v>
+        <v>3389</v>
       </c>
       <c r="E3" t="n">
-        <v>246</v>
+        <v>564.8333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -855,13 +915,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>56685</v>
+        <v>30849</v>
       </c>
       <c r="E4" t="n">
-        <v>4723.75</v>
+        <v>3856.125</v>
       </c>
     </row>
     <row r="5">
@@ -876,13 +936,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>30341</v>
+        <v>26406</v>
       </c>
       <c r="E5" t="n">
-        <v>2758.272727272727</v>
+        <v>1650.375</v>
       </c>
     </row>
     <row r="6">
@@ -900,10 +960,10 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>16659</v>
+        <v>15546</v>
       </c>
       <c r="E6" t="n">
-        <v>1388.25</v>
+        <v>1295.5</v>
       </c>
     </row>
     <row r="7">
@@ -918,13 +978,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>4474</v>
+        <v>6480</v>
       </c>
       <c r="E7" t="n">
-        <v>745.6666666666666</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -939,13 +999,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>10241</v>
+        <v>5885</v>
       </c>
       <c r="E8" t="n">
-        <v>853.4166666666666</v>
+        <v>840.7142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -960,13 +1020,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>493</v>
+        <v>4419</v>
       </c>
       <c r="E9" t="n">
-        <v>246.5</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10">
@@ -981,13 +1041,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>500</v>
+        <v>3513</v>
       </c>
       <c r="E10" t="n">
-        <v>250</v>
+        <v>439.125</v>
       </c>
     </row>
     <row r="11">
@@ -1002,13 +1062,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>880</v>
+        <v>778</v>
       </c>
       <c r="E11" t="n">
-        <v>440</v>
+        <v>259.3333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1023,13 +1083,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>21387</v>
+        <v>14085</v>
       </c>
       <c r="E12" t="n">
-        <v>7129</v>
+        <v>7042.5</v>
       </c>
     </row>
     <row r="13">
@@ -1044,13 +1104,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>54863</v>
+        <v>109948</v>
       </c>
       <c r="E13" t="n">
-        <v>5486.3</v>
+        <v>7329.866666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1065,13 +1125,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>23788</v>
+        <v>22306</v>
       </c>
       <c r="E14" t="n">
-        <v>2643.111111111111</v>
+        <v>3186.571428571428</v>
       </c>
     </row>
     <row r="15">
@@ -1086,13 +1146,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>12987</v>
+        <v>5146</v>
       </c>
       <c r="E15" t="n">
-        <v>3246.75</v>
+        <v>857.6666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -1144,13 +1204,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.638</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.708</v>
+        <v>-0.675</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -1160,13 +1220,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.782</v>
+        <v>-0.857</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.805</v>
+        <v>-0.852</v>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1229,13 +1289,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.8</v>
+        <v>35.8</v>
       </c>
       <c r="D2" t="n">
-        <v>4724</v>
+        <v>3856</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1250,13 +1310,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43.8</v>
+        <v>66.2</v>
       </c>
       <c r="D3" t="n">
-        <v>5486</v>
+        <v>7330</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1314,17 +1374,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39–76 元</t>
+          <t>49–98 元</t>
         </is>
       </c>
     </row>
@@ -1335,17 +1395,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58–112 元</t>
+          <t>57–135 元</t>
         </is>
       </c>
     </row>
@@ -1415,16 +1475,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>56685</v>
+        <v>30849</v>
       </c>
       <c r="E2" t="n">
-        <v>4723.75</v>
+        <v>3856.125</v>
       </c>
       <c r="F2" t="n">
-        <v>51.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="3">
@@ -1439,16 +1499,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>30341</v>
+        <v>26406</v>
       </c>
       <c r="E3" t="n">
-        <v>2758.272727272727</v>
+        <v>1650.375</v>
       </c>
       <c r="F3" t="n">
-        <v>27.7</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="4">
@@ -1466,13 +1526,13 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>16659</v>
+        <v>15546</v>
       </c>
       <c r="E4" t="n">
-        <v>1388.25</v>
+        <v>1295.5</v>
       </c>
       <c r="F4" t="n">
-        <v>15.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1487,16 +1547,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4474</v>
+        <v>6480</v>
       </c>
       <c r="E5" t="n">
-        <v>745.6666666666666</v>
+        <v>648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -1511,16 +1571,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1073</v>
+        <v>3526</v>
       </c>
       <c r="E6" t="n">
-        <v>536.5</v>
+        <v>587.6666666666666</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7">
@@ -1535,16 +1595,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>246</v>
+        <v>3389</v>
       </c>
       <c r="E7" t="n">
-        <v>246</v>
+        <v>564.8333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
@@ -1559,16 +1619,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>54863</v>
+        <v>109948</v>
       </c>
       <c r="E8" t="n">
-        <v>5486.3</v>
+        <v>7329.866666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>43.8</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="9">
@@ -1583,16 +1643,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>23788</v>
+        <v>22306</v>
       </c>
       <c r="E9" t="n">
-        <v>2643.111111111111</v>
+        <v>3186.571428571428</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="10">
@@ -1607,16 +1667,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>21387</v>
+        <v>14085</v>
       </c>
       <c r="E10" t="n">
-        <v>7129</v>
+        <v>7042.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="11">
@@ -1627,20 +1687,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80-99</t>
+          <t>100-119</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>12987</v>
+        <v>5885</v>
       </c>
       <c r="E11" t="n">
-        <v>3246.75</v>
+        <v>840.7142857142857</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
@@ -1651,20 +1711,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>80-99</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>10241</v>
+        <v>5146</v>
       </c>
       <c r="E12" t="n">
-        <v>853.4166666666666</v>
+        <v>857.6666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -1675,20 +1735,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160-179</t>
+          <t>120-139</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>880</v>
+        <v>4419</v>
       </c>
       <c r="E13" t="n">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -1703,16 +1763,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>500</v>
+        <v>3513</v>
       </c>
       <c r="E14" t="n">
-        <v>250</v>
+        <v>439.125</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -1723,20 +1783,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>120-139</t>
+          <t>160-179</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>493</v>
+        <v>778</v>
       </c>
       <c r="E15" t="n">
-        <v>246.5</v>
+        <v>259.3333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1763,7 +1823,7 @@
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
@@ -1902,7 +1962,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -1969,7 +2029,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -2036,7 +2096,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -2103,7 +2163,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -2170,7 +2230,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -2237,7 +2297,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -2267,7 +2327,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>无品牌 情侣款polo衫 半袖 潮流 纯色</t>
+          <t>无品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2304,7 +2364,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2371,7 +2431,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2438,7 +2498,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2505,7 +2565,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2572,7 +2632,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2639,7 +2699,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2669,7 +2729,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>无品牌 情侣款polo衫 半袖 潮流 纯色</t>
+          <t>无品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2706,7 +2766,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2773,7 +2833,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2840,7 +2900,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2870,7 +2930,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>无品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2897,7 +2957,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>拼多多示范店铺86</t>
+          <t>拼多多示范店铺52</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2907,7 +2967,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2937,7 +2997,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>无品牌 情侣款polo衫 半袖 潮流 纯色</t>
+          <t>白牌 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2946,13 +3006,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G18" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="H18" t="n">
-        <v>7312</v>
+        <v>2177</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2960,11 +3020,11 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2120</v>
+        <v>541</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>拼多多示范店铺1</t>
+          <t>拼多多示范店铺30</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2974,15 +3034,15 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.864036182725775</v>
+        <v>3.337858429041094</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3064,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>白牌 重磅珠地棉polo衫 免烫 通勤百搭</t>
+          <t>白牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3013,13 +3073,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H19" t="n">
-        <v>2609</v>
+        <v>5782</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3027,11 +3087,11 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>761</v>
+        <v>2793</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>拼多多示范店铺36</t>
+          <t>拼多多示范店铺66</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3041,11 +3101,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.416474079100221</v>
+        <v>3.762078087334639</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3071,22 +3131,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>白牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>无品牌 针织polo衫 薄款 透气 中青年</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>工厂直供</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H20" t="n">
-        <v>6864</v>
+        <v>3576</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3094,11 +3154,11 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3527</v>
+        <v>2053</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>拼多多示范店铺56</t>
+          <t>拼多多示范店铺25</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3108,11 +3168,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.836577274840649</v>
+        <v>3.55339751012388</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3138,7 +3198,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>白牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
+          <t>白牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3147,13 +3207,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="H21" t="n">
-        <v>5443</v>
+        <v>766</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3161,11 +3221,11 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2969</v>
+        <v>262</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>拼多多示范店铺44</t>
+          <t>拼多多示范店铺83</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3175,15 +3235,15 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.735838334317074</v>
+        <v>2.884228769632604</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
@@ -3214,13 +3274,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H22" t="n">
-        <v>2496</v>
+        <v>1109</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3228,11 +3288,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>639</v>
+        <v>332</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>拼多多示范店铺57</t>
+          <t>拼多多示范店铺36</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3242,11 +3302,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.397244581010386</v>
+        <v>3.04493154614916</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3272,7 +3332,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>无品牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
+          <t>白牌 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3281,13 +3341,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H23" t="n">
-        <v>2120</v>
+        <v>2849</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3295,11 +3355,11 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>882</v>
+        <v>656</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>拼多多示范店铺63</t>
+          <t>拼多多示范店铺70</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3309,22 +3369,22 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.326335860928751</v>
+        <v>3.454692449239477</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REF0024</t>
+          <t>REF0023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3339,7 +3399,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>白牌 情侣款polo衫 半袖 潮流 纯色</t>
+          <t>无品牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3348,13 +3408,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H24" t="n">
-        <v>5715</v>
+        <v>1391</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3362,11 +3422,11 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1821</v>
+        <v>397</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>拼多多示范店铺8</t>
+          <t>拼多多示范店铺50</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3376,11 +3436,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.757016234731301</v>
+        <v>3.143327129992046</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3391,7 +3451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REF0025</t>
+          <t>REF0026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3406,7 +3466,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>白牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>工厂直供 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3415,13 +3475,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H25" t="n">
-        <v>6784</v>
+        <v>2637</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3429,11 +3489,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1511</v>
+        <v>1155</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>拼多多示范店铺87</t>
+          <t>拼多多示范店铺73</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3443,11 +3503,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.831485839248657</v>
+        <v>3.421110129793434</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3458,7 +3518,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REF0026</t>
+          <t>REF0027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3473,7 +3533,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>白牌 情侣款polo衫 半袖 潮流 纯色</t>
+          <t>无品牌 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3482,13 +3542,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H26" t="n">
-        <v>7606</v>
+        <v>6182</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3496,11 +3556,11 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4386</v>
+        <v>2680</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>拼多多示范店铺54</t>
+          <t>拼多多示范店铺41</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3510,22 +3570,22 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.881156321075564</v>
+        <v>3.791129000727286</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>20-39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REF0027</t>
+          <t>REF0028</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3540,7 +3600,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
+          <t>白牌 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3549,13 +3609,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="H27" t="n">
-        <v>5925</v>
+        <v>1706</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3563,11 +3623,11 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2772</v>
+        <v>800</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>拼多多示范店铺83</t>
+          <t>拼多多示范店铺80</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3577,22 +3637,22 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.772688354682141</v>
+        <v>3.231979026831504</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>REF0028</t>
+          <t>REF0029</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3607,7 +3667,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>白牌 针织polo衫 薄款 透气 中青年</t>
+          <t>无品牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3616,13 +3676,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G28" t="n">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="H28" t="n">
-        <v>6746</v>
+        <v>550</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3630,11 +3690,11 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3378</v>
+        <v>168</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>拼多多示范店铺28</t>
+          <t>拼多多示范店铺21</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3644,22 +3704,22 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.829046336853183</v>
+        <v>2.740362689494244</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REF0029</t>
+          <t>REF0030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3674,7 +3734,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>自主品牌 针织polo衫 薄款 透气 中青年</t>
+          <t>白牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3683,13 +3743,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H29" t="n">
-        <v>5651</v>
+        <v>4482</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3697,11 +3757,11 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1682</v>
+        <v>1439</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>拼多多示范店铺84</t>
+          <t>拼多多示范店铺71</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3711,11 +3771,11 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.752125307297898</v>
+        <v>3.651471852199041</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3726,12 +3786,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REF0030</t>
+          <t>REF0031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>抖音</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3741,7 +3801,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>无品牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
+          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3750,13 +3810,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="H30" t="n">
-        <v>5529</v>
+        <v>1950</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3764,11 +3824,11 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2332</v>
+        <v>862</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>拼多多示范店铺14</t>
+          <t>抖音示范店铺33</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3778,22 +3838,22 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.742646589938736</v>
+        <v>3.290034611362518</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REF0031</t>
+          <t>REF0032</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3808,7 +3868,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
+          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3817,13 +3877,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="H31" t="n">
-        <v>1119</v>
+        <v>335</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3831,11 +3891,11 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>377</v>
+        <v>104</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>抖音示范店铺7</t>
+          <t>抖音示范店铺57</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3845,22 +3905,22 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.04883008652835</v>
+        <v>2.525044807036845</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REF0032</t>
+          <t>REF0033</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3875,7 +3935,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>白牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3884,13 +3944,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G32" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H32" t="n">
-        <v>1006</v>
+        <v>3186</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3898,11 +3958,11 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>313</v>
+        <v>1380</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>抖音示范店铺57</t>
+          <t>抖音示范店铺6</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3912,11 +3972,11 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.002597980719909</v>
+        <v>3.503245771465113</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3927,7 +3987,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REF0033</t>
+          <t>REF0034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3942,22 +4002,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>白牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>工厂直供 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>无品牌</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G33" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H33" t="n">
-        <v>3186</v>
+        <v>2719</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3965,11 +4025,11 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1380</v>
+        <v>815</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>抖音示范店铺6</t>
+          <t>抖音示范店铺31</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3979,22 +4039,22 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.503245771465113</v>
+        <v>3.4344092075875</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REF0034</t>
+          <t>REF0035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4009,22 +4069,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>工厂直供 情侣款polo衫 半袖 潮流 纯色</t>
+          <t>工厂直供 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>无品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="G34" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="H34" t="n">
-        <v>2719</v>
+        <v>778</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4032,11 +4092,11 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>815</v>
+        <v>401</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>抖音示范店铺31</t>
+          <t>抖音示范店铺59</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4046,22 +4106,22 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.4344092075875</v>
+        <v>2.890979596989689</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>100-119</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REF0035</t>
+          <t>REF0036</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4076,7 +4136,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>工厂直供 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
+          <t>无品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4085,13 +4145,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="G35" t="n">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="H35" t="n">
-        <v>778</v>
+        <v>1361</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4099,11 +4159,11 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>401</v>
+        <v>747</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>抖音示范店铺59</t>
+          <t>抖音示范店铺36</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4113,22 +4173,22 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.890979596989689</v>
+        <v>3.133858125203335</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>20-39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REF0036</t>
+          <t>REF0037</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4143,7 +4203,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>工厂直供 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>自主品牌 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4152,13 +4212,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="G36" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="H36" t="n">
-        <v>1361</v>
+        <v>306</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4166,11 +4226,11 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>747</v>
+        <v>110</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>抖音示范店铺9</t>
+          <t>抖音示范店铺34</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4180,22 +4240,22 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.133858125203335</v>
+        <v>2.48572142648158</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>100-119</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REF0037</t>
+          <t>REF0038</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4210,22 +4270,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>白牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
+          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>自主品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="H37" t="n">
-        <v>1157</v>
+        <v>2341</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4233,11 +4293,11 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>685</v>
+        <v>875</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>抖音示范店铺23</t>
+          <t>抖音示范店铺66</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4247,22 +4307,22 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.06333335895175</v>
+        <v>3.369401413696624</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>80-99</t>
+          <t>20-39</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>REF0038</t>
+          <t>REF0039</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4277,22 +4337,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>工厂直供 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
+          <t>无品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>无品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="H38" t="n">
-        <v>792</v>
+        <v>521</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4300,11 +4360,11 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>抖音示范店铺33</t>
+          <t>抖音示范店铺9</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4314,22 +4374,22 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.898725181589493</v>
+        <v>2.716837723299525</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>100-119</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>REF0039</t>
+          <t>REF0040</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4344,7 +4404,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>自主品牌 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4353,13 +4413,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H39" t="n">
-        <v>879</v>
+        <v>922</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4367,11 +4427,11 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>417</v>
+        <v>230</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>抖音示范店铺86</t>
+          <t>抖音示范店铺42</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4381,11 +4441,11 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.943988875073772</v>
+        <v>2.964730921053629</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4396,7 +4456,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REF0040</t>
+          <t>REF0041</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4411,7 +4471,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>自主品牌 重磅珠地棉polo衫 免烫 通勤百搭</t>
+          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4420,13 +4480,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="G40" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H40" t="n">
-        <v>3498</v>
+        <v>1124</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4434,11 +4494,11 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1628</v>
+        <v>648</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>抖音示范店铺42</t>
+          <t>抖音示范店铺1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4448,22 +4508,22 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.543819805142658</v>
+        <v>3.050766311233042</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REF0041</t>
+          <t>REF0042</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4478,7 +4538,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4487,13 +4547,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="H41" t="n">
-        <v>1124</v>
+        <v>852</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4501,11 +4561,11 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>648</v>
+        <v>438</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>抖音示范店铺1</t>
+          <t>抖音示范店铺87</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4515,22 +4575,22 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.050766311233042</v>
+        <v>2.9304395947667</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>REF0042</t>
+          <t>REF0043</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4545,7 +4605,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
+          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4554,13 +4614,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H42" t="n">
-        <v>852</v>
+        <v>1269</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4568,11 +4628,11 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>抖音示范店铺87</t>
+          <t>抖音示范店铺26</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4582,11 +4642,11 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.9304395947667</v>
+        <v>3.103461622094705</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4597,7 +4657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>REF0043</t>
+          <t>REF0044</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4612,7 +4672,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>自主品牌 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>工厂直供 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4621,13 +4681,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G43" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H43" t="n">
-        <v>1269</v>
+        <v>1238</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4635,11 +4695,11 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>424</v>
+        <v>686</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>抖音示范店铺26</t>
+          <t>抖音示范店铺32</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4649,22 +4709,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.103461622094705</v>
+        <v>3.0927206446841</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>REF0044</t>
+          <t>REF0045</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4679,7 +4739,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>工厂直供 针织polo衫 薄款 透气 中青年</t>
+          <t>无品牌 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4688,13 +4748,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G44" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H44" t="n">
-        <v>1238</v>
+        <v>222</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4702,11 +4762,11 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>686</v>
+        <v>106</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>抖音示范店铺19</t>
+          <t>抖音示范店铺59</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4716,11 +4776,11 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.0927206446841</v>
+        <v>2.346352974450639</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4731,12 +4791,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>REF0045</t>
+          <t>REF0046</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4746,7 +4806,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>工厂直供 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
+          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4755,13 +4815,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="G45" t="n">
-        <v>94</v>
+        <v>193</v>
       </c>
       <c r="H45" t="n">
-        <v>4069</v>
+        <v>230</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4769,11 +4829,11 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>987</v>
+        <v>95</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>抖音示范店铺32</t>
+          <t>微信视频号示范店铺93</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4783,52 +4843,52 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.609487689853285</v>
+        <v>2.361727836017593</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>REF0046</t>
+          <t>REF0047</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>自主品牌 针织polo衫 薄款 透气 中青年</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>自主品牌</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G46" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="H46" t="n">
-        <v>184</v>
+        <v>1115</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4836,11 +4896,11 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>76</v>
+        <v>294</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>淘宝示范店铺93</t>
+          <t>微信视频号示范店铺99</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4850,11 +4910,11 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.264817823009536</v>
+        <v>3.047274867384179</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4865,37 +4925,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>REF0047</t>
+          <t>REF0048</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>自主品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>自主品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="G47" t="n">
-        <v>244</v>
+        <v>109</v>
       </c>
       <c r="H47" t="n">
-        <v>441</v>
+        <v>2281</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4903,11 +4963,11 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>116</v>
+        <v>674</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>淘宝示范店铺99</t>
+          <t>微信视频号示范店铺43</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4917,37 +4977,37 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.644438589467839</v>
+        <v>3.358125285276649</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>160-179</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>REF0048</t>
+          <t>REF0049</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>无品牌 锥形牛仔裤 九分 春夏薄款</t>
+          <t>工厂直供 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4956,13 +5016,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="G48" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="H48" t="n">
-        <v>767</v>
+        <v>813</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4970,11 +5030,11 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>227</v>
+        <v>388</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>淘宝示范店铺41</t>
+          <t>微信视频号示范店铺70</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4984,52 +5044,52 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.884795363948981</v>
+        <v>2.910090545594068</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>REF0049</t>
+          <t>REF0050</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>白牌 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>工厂直供</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G49" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H49" t="n">
-        <v>166</v>
+        <v>450</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5037,11 +5097,11 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>43</v>
+        <v>240</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>淘宝示范店铺60</t>
+          <t>微信视频号示范店铺62</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5051,52 +5111,52 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.220108088040055</v>
+        <v>2.653212513775344</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>140-159</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>REF0050</t>
+          <t>REF0051</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>白牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>无品牌 情侣款polo衫 半袖 潮流 纯色</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>工厂直供</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G50" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H50" t="n">
-        <v>342</v>
+        <v>1097</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5104,11 +5164,11 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>126</v>
+        <v>547</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>淘宝示范店铺62</t>
+          <t>微信视频号示范店铺35</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5118,52 +5178,52 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.534026106056135</v>
+        <v>3.040206627574712</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>REF0051</t>
+          <t>REF0052</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>无品牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>无品牌 针织polo衫 薄款 透气 中青年</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>无品牌</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="H51" t="n">
-        <v>439</v>
+        <v>847</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5171,11 +5231,11 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>淘宝示范店铺35</t>
+          <t>微信视频号示范店铺80</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5185,52 +5245,52 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.642464520242121</v>
+        <v>2.927883410330707</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>160-179</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REF0052</t>
+          <t>REF0053</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>无品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>无品牌 针织polo衫 薄款 透气 中青年</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>无品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="G52" t="n">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="H52" t="n">
-        <v>309</v>
+        <v>3234</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5238,11 +5298,11 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>103</v>
+        <v>755</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>淘宝示范店铺80</t>
+          <t>微信视频号示范店铺49</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5252,37 +5312,37 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.489958479424835</v>
+        <v>3.509740015570382</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>120-139</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>REF0053</t>
+          <t>REF0054</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>无品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5291,13 +5351,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="G53" t="n">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="H53" t="n">
-        <v>1035</v>
+        <v>903</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5305,11 +5365,11 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>淘宝示范店铺49</t>
+          <t>微信视频号示范店铺11</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5319,37 +5379,37 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.014940349792937</v>
+        <v>2.955687750313506</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>REF0054</t>
+          <t>REF0055</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>无品牌 冰丝polo衫 男 夏季 翻领短袖 商务休闲</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5358,13 +5418,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="G54" t="n">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="H54" t="n">
-        <v>314</v>
+        <v>1853</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5372,11 +5432,11 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>105</v>
+        <v>1080</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>淘宝示范店铺11</t>
+          <t>微信视频号示范店铺3</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5386,37 +5446,37 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.496929648073215</v>
+        <v>3.267875419318897</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>REF0055</t>
+          <t>REF0056</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>无品牌 牛仔裤 男 直筒 宽松 大码 百搭</t>
+          <t>工厂直供 纯棉polo衫 女 宽松显瘦 短袖上衣</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5425,13 +5485,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="G55" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="H55" t="n">
-        <v>568</v>
+        <v>893</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5439,11 +5499,11 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>淘宝示范店铺3</t>
+          <t>微信视频号示范店铺99</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5453,37 +5513,37 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.754348335711019</v>
+        <v>2.950851458888546</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>100-119</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REF0056</t>
+          <t>REF0057</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>工厂直供 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+          <t>工厂直供 重磅珠地棉polo衫 免烫 通勤百搭</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5492,13 +5552,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="G56" t="n">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="H56" t="n">
-        <v>334</v>
+        <v>2203</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5506,11 +5566,11 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>130</v>
+        <v>715</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>淘宝示范店铺99</t>
+          <t>微信视频号示范店铺92</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5520,37 +5580,37 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.523746466811565</v>
+        <v>3.343014497150768</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>140-159</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>REF0057</t>
+          <t>REF0058</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>自主品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5559,13 +5619,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="G57" t="n">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="H57" t="n">
-        <v>725</v>
+        <v>251</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5573,11 +5633,11 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>淘宝示范店铺92</t>
+          <t>微信视频号示范店铺73</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5587,15 +5647,15 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.860338006570994</v>
+        <v>2.399673721481038</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>80-99</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
@@ -5607,17 +5667,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>工厂直供 针织polo衫 薄款 透气 中青年</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5626,13 +5686,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="G58" t="n">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="H58" t="n">
-        <v>312</v>
+        <v>733</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5640,11 +5700,11 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>124</v>
+        <v>295</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>淘宝示范店铺56</t>
+          <t>微信视频号示范店铺47</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5654,15 +5714,15 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.494154594018443</v>
+        <v>2.865103974641128</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>100-119</t>
         </is>
       </c>
     </row>
@@ -5674,17 +5734,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>微信视频号</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>polo衫</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>工厂直供 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>自主品牌 中老年polo衫 爸爸装 冰丝短袖 舒适透气</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5693,13 +5753,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="G59" t="n">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="H59" t="n">
-        <v>205</v>
+        <v>3331</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5707,11 +5767,11 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>94</v>
+        <v>1609</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>淘宝示范店铺94</t>
+          <t>微信视频号示范店铺69</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5721,15 +5781,15 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.311753861055754</v>
+        <v>3.522574632691177</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5801,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5751,22 +5811,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>自主品牌 牛仔裤 男 直筒 宽松 大码 百搭</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>无品牌</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="G60" t="n">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="H60" t="n">
-        <v>6266</v>
+        <v>650</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5774,11 +5834,11 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>3134</v>
+        <v>214</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>拼多多示范店铺42</t>
+          <t>淘宝示范店铺97</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5788,15 +5848,15 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3.796990390545687</v>
+        <v>2.812913356642856</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5868,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5818,7 +5878,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>自主品牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>无品牌 锥形牛仔裤 九分 春夏薄款</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5827,13 +5887,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="G61" t="n">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="H61" t="n">
-        <v>5551</v>
+        <v>531</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5841,11 +5901,11 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2882</v>
+        <v>187</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>拼多多示范店铺67</t>
+          <t>淘宝示范店铺46</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5855,15 +5915,15 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3.744371227331861</v>
+        <v>2.725094521081469</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5935,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5885,7 +5945,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>白牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5894,13 +5954,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="G62" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="H62" t="n">
-        <v>8256</v>
+        <v>966</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5908,11 +5968,11 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4155</v>
+        <v>300</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>拼多多示范店铺38</t>
+          <t>淘宝示范店铺53</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5922,15 +5982,15 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.916769684283136</v>
+        <v>2.984977126415493</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
@@ -5942,7 +6002,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5952,7 +6012,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5961,13 +6021,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="G63" t="n">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="H63" t="n">
-        <v>2982</v>
+        <v>494</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5975,11 +6035,11 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>962</v>
+        <v>235</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>拼多多示范店铺96</t>
+          <t>淘宝示范店铺38</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5989,15 +6049,15 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3.474507639116976</v>
+        <v>2.693726948923647</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6069,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6019,7 +6079,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>白牌 锥形牛仔裤 九分 春夏薄款</t>
+          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6028,13 +6088,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="G64" t="n">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="H64" t="n">
-        <v>9134</v>
+        <v>188</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6042,11 +6102,11 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>2669</v>
+        <v>73</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>拼多多示范店铺98</t>
+          <t>淘宝示范店铺59</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6056,27 +6116,27 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3.960661007270982</v>
+        <v>2.27415784926368</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>REF0066</t>
+          <t>REF0067</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6086,22 +6146,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>自主品牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>自主品牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>无品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G65" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H65" t="n">
-        <v>9271</v>
+        <v>1911</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6109,11 +6169,11 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>4593</v>
+        <v>599</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>拼多多示范店铺38</t>
+          <t>淘宝示范店铺23</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6123,27 +6183,27 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3.967126581076413</v>
+        <v>3.281260687055013</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>REF0067</t>
+          <t>REF0068</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6153,22 +6213,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>自主品牌 牛仔裤 男 直筒 宽松 大码 百搭</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>自主品牌</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="G66" t="n">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="H66" t="n">
-        <v>7548</v>
+        <v>163</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -6176,11 +6236,11 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1891</v>
+        <v>41</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>拼多多示范店铺61</t>
+          <t>淘宝示范店铺17</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6190,27 +6250,27 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>3.877831891492894</v>
+        <v>2.212187604403958</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>REF0068</t>
+          <t>REF0069</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6220,22 +6280,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>工厂直供</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="G67" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="H67" t="n">
-        <v>4877</v>
+        <v>386</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6243,11 +6303,11 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>2859</v>
+        <v>130</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>拼多多示范店铺63</t>
+          <t>淘宝示范店铺9</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6257,27 +6317,27 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>3.688152755591566</v>
+        <v>2.586587304671755</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>80-99</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>REF0069</t>
+          <t>REF0070</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6287,22 +6347,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>无品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>自主品牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>工厂直供</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G68" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H68" t="n">
-        <v>4056</v>
+        <v>570</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6310,11 +6370,11 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>2424</v>
+        <v>258</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>拼多多示范店铺58</t>
+          <t>淘宝示范店铺32</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6324,11 +6384,11 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>3.60809794632528</v>
+        <v>2.755874855672491</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6339,12 +6399,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>REF0070</t>
+          <t>REF0071</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6354,7 +6414,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>白牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6363,13 +6423,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="G69" t="n">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="H69" t="n">
-        <v>8701</v>
+        <v>288</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -6377,11 +6437,11 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>3789</v>
+        <v>84</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>拼多多示范店铺95</t>
+          <t>淘宝示范店铺76</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6391,27 +6451,27 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>3.939569168655902</v>
+        <v>2.459392487759231</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>160-179</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>REF0071</t>
+          <t>REF0072</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6421,7 +6481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>白牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+          <t>无品牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6430,13 +6490,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="G70" t="n">
-        <v>93</v>
+        <v>268</v>
       </c>
       <c r="H70" t="n">
-        <v>4120</v>
+        <v>251</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6444,11 +6504,11 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>958</v>
+        <v>125</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>拼多多示范店铺53</t>
+          <t>淘宝示范店铺11</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6458,27 +6518,27 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>3.614897216033135</v>
+        <v>2.399673721481038</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>160-179</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>REF0072</t>
+          <t>REF0073</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6488,7 +6548,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>自主品牌 中老年牛仔裤 宽松直筒 高腰 舒适</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6497,13 +6557,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="G71" t="n">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="H71" t="n">
-        <v>3743</v>
+        <v>250</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6511,11 +6571,11 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>1185</v>
+        <v>79</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>拼多多示范店铺30</t>
+          <t>淘宝示范店铺59</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6525,27 +6585,27 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>3.573219827114422</v>
+        <v>2.397940008672037</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>140-159</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>REF0073</t>
+          <t>REF0074</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6564,13 +6624,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="G72" t="n">
-        <v>99</v>
+        <v>223</v>
       </c>
       <c r="H72" t="n">
-        <v>4679</v>
+        <v>151</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6578,11 +6638,11 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>2683</v>
+        <v>46</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>拼多多示范店铺35</t>
+          <t>淘宝示范店铺70</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6592,27 +6652,27 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>3.67015304519218</v>
+        <v>2.178976947293169</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>140-159</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>REF0074</t>
+          <t>REF0075</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6622,7 +6682,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>自主品牌 加绒牛仔裤 秋冬 保暖 直筒</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6631,13 +6691,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="G73" t="n">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="H73" t="n">
-        <v>5987</v>
+        <v>245</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6645,11 +6705,11 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2991</v>
+        <v>55</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>拼多多示范店铺89</t>
+          <t>淘宝示范店铺60</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6659,22 +6719,22 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>3.777209258145685</v>
+        <v>2.389166084364533</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>20-39</t>
+          <t>120-139</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>REF0075</t>
+          <t>REF0076</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6689,7 +6749,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6698,13 +6758,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G74" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H74" t="n">
-        <v>4796</v>
+        <v>9373</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6712,11 +6772,11 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>1799</v>
+        <v>5409</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>拼多多示范店铺4</t>
+          <t>拼多多示范店铺6</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6726,11 +6786,11 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3.680879174426811</v>
+        <v>3.971878617026266</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6741,12 +6801,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>REF0076</t>
+          <t>REF0077</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6756,22 +6816,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>白牌 锥形牛仔裤 九分 春夏薄款</t>
+          <t>白牌 加绒牛仔裤 秋冬 保暖 直筒</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>无品牌</t>
+          <t>自主品牌</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="G75" t="n">
-        <v>183</v>
+        <v>99</v>
       </c>
       <c r="H75" t="n">
-        <v>1592</v>
+        <v>4118</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6779,11 +6839,11 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>924</v>
+        <v>1201</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>抖音示范店铺61</t>
+          <t>拼多多示范店铺74</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6793,27 +6853,27 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>3.20194306340165</v>
+        <v>3.614686342282013</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>REF0077</t>
+          <t>REF0079</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6823,7 +6883,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6832,13 +6892,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G76" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H76" t="n">
-        <v>1846</v>
+        <v>3482</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6846,11 +6906,11 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1085</v>
+        <v>842</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>抖音示范店铺14</t>
+          <t>拼多多示范店铺52</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6860,27 +6920,27 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>3.266231696689893</v>
+        <v>3.541828766781312</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>40-59</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REF0078</t>
+          <t>REF0080</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6890,22 +6950,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>白牌 锥形牛仔裤 九分 春夏薄款</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>白牌</t>
+          <t>工厂直供</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="G77" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="H77" t="n">
-        <v>2416</v>
+        <v>13909</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6913,11 +6973,11 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1154</v>
+        <v>5312</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>抖音示范店铺41</t>
+          <t>拼多多示范店铺66</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6927,27 +6987,27 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>3.383096929949094</v>
+        <v>4.143295907124072</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>80-99</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>REF0079</t>
+          <t>REF0081</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6966,13 +7026,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G78" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="H78" t="n">
-        <v>2576</v>
+        <v>12587</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6980,11 +7040,11 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>571</v>
+        <v>2790</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>抖音示范店铺98</t>
+          <t>拼多多示范店铺98</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6994,27 +7054,27 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3.410945858687775</v>
+        <v>4.099922232196922</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>80-99</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>REF0080</t>
+          <t>REF0082</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7024,7 +7084,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>工厂直供 中老年牛仔裤 宽松直筒 高腰 舒适</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7033,13 +7093,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="G79" t="n">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="H79" t="n">
-        <v>561</v>
+        <v>3810</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7047,11 +7107,11 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>142</v>
+        <v>962</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>抖音示范店铺81</t>
+          <t>拼多多示范店铺81</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7061,27 +7121,27 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.748962861256162</v>
+        <v>3.580924975675619</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>REF0081</t>
+          <t>REF0083</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7100,13 +7160,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="G80" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="H80" t="n">
-        <v>924</v>
+        <v>4209</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7114,11 +7174,11 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>389</v>
+        <v>1772</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>抖音示范店铺64</t>
+          <t>拼多多示范店铺64</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7128,27 +7188,27 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.965671971220107</v>
+        <v>3.624178925748022</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>20-39</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>REF0082</t>
+          <t>REF0084</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7167,13 +7227,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G81" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="H81" t="n">
-        <v>3174</v>
+        <v>14460</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7181,11 +7241,11 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1530</v>
+        <v>6972</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>抖音示范店铺71</t>
+          <t>拼多多示范店铺71</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7195,27 +7255,27 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>3.501606922418829</v>
+        <v>4.160168292958512</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>REF0083</t>
+          <t>REF0085</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7234,13 +7294,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="G82" t="n">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="H82" t="n">
-        <v>1534</v>
+        <v>7961</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7248,11 +7308,11 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>391</v>
+        <v>2027</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>抖音示范店铺1</t>
+          <t>拼多多示范店铺1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7262,27 +7322,27 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>3.185825359612962</v>
+        <v>3.900967623919125</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>REF0084</t>
+          <t>REF0086</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7301,13 +7361,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="G83" t="n">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="H83" t="n">
-        <v>746</v>
+        <v>3868</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -7315,11 +7375,11 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>324</v>
+        <v>1682</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>抖音示范店铺62</t>
+          <t>拼多多示范店铺62</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7329,27 +7389,27 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.872738827472669</v>
+        <v>3.587486465410964</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>REF0085</t>
+          <t>REF0087</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7359,7 +7419,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>工厂直供 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+          <t>无品牌 中老年牛仔裤 宽松直筒 高腰 舒适</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7368,13 +7428,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="G84" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="H84" t="n">
-        <v>2212</v>
+        <v>9876</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7382,11 +7442,11 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>727</v>
+        <v>3246</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>抖音示范店铺53</t>
+          <t>拼多多示范店铺30</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7396,27 +7456,27 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>3.344785122632661</v>
+        <v>3.994581081259895</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>60-79</t>
+          <t>20-39</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>REF0086</t>
+          <t>REF0088</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7426,7 +7486,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>工厂直供 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7435,13 +7495,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="G85" t="n">
-        <v>174</v>
+        <v>90</v>
       </c>
       <c r="H85" t="n">
-        <v>2025</v>
+        <v>7207</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7449,11 +7509,11 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>718</v>
+        <v>2359</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>抖音示范店铺65</t>
+          <t>拼多多示范店铺64</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7463,27 +7523,27 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>3.306425027550687</v>
+        <v>3.857754522059442</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>60-79</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>REF0087</t>
+          <t>REF0089</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7493,22 +7553,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>工厂直供 锥形牛仔裤 九分 春夏薄款</t>
+          <t>工厂直供 牛仔裤 男 直筒 宽松 大码 百搭</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>工厂直供</t>
+          <t>白牌</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="G86" t="n">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c r="H86" t="n">
-        <v>445</v>
+        <v>9996</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7516,11 +7576,11 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>160</v>
+        <v>2400</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>抖音示范店铺70</t>
+          <t>拼多多示范店铺19</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7530,27 +7590,27 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.648360010980932</v>
+        <v>3.999826247454413</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>REF0088</t>
+          <t>REF0090</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7560,7 +7620,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>自主品牌 锥形牛仔裤 九分 春夏薄款</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7569,13 +7629,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="G87" t="n">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="H87" t="n">
-        <v>7270</v>
+        <v>5468</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -7583,11 +7643,11 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>4355</v>
+        <v>1431</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>抖音示范店铺57</t>
+          <t>拼多多示范店铺51</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7597,22 +7657,22 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>3.861534410859038</v>
+        <v>3.737828505895785</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>80-99</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>REF0089</t>
+          <t>REF0091</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7627,7 +7687,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>无品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+          <t>白牌 加绒牛仔裤 秋冬 保暖 直筒</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7636,13 +7696,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="G88" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="H88" t="n">
-        <v>538</v>
+        <v>2300</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -7650,11 +7710,11 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>120</v>
+        <v>1121</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>抖音示范店铺53</t>
+          <t>抖音示范店铺31</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7664,22 +7724,22 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-08-19T22:51:32</t>
+          <t>2026-08-19T23:14:43</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.730782275666389</v>
+        <v>3.361727836017593</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>100-119</t>
+          <t>40-59</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>REF0090</t>
+          <t>REF0092</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7694,52 +7754,1861 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>49</v>
+      </c>
+      <c r="G89" t="n">
+        <v>72</v>
+      </c>
+      <c r="H89" t="n">
+        <v>14350</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>8595</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>抖音示范店铺57</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>4.156851901070011</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>REF0093</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>无品牌 阔腿牛仔裤 复古 水洗 做旧</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>白牌</t>
         </is>
       </c>
-      <c r="F89" t="n">
+      <c r="F90" t="n">
+        <v>102</v>
+      </c>
+      <c r="G90" t="n">
+        <v>138</v>
+      </c>
+      <c r="H90" t="n">
+        <v>538</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>120</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>抖音示范店铺53</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>2.730782275666389</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>REF0094</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>无品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
         <v>111</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G91" t="n">
         <v>141</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H91" t="n">
         <v>1172</v>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>近30天</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
         <v>314</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>抖音示范店铺75</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-08-19T22:51:32</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
         <v>3.068927611682072</v>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>REF0095</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>无品牌 锥形牛仔裤 九分 春夏薄款</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>110</v>
+      </c>
+      <c r="G92" t="n">
+        <v>164</v>
+      </c>
+      <c r="H92" t="n">
+        <v>648</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>132</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>抖音示范店铺45</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>2.811575005870593</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>REF0096</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>无品牌 牛仔裤 男 直筒 宽松 大码 百搭</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>115</v>
+      </c>
+      <c r="G93" t="n">
+        <v>173</v>
+      </c>
+      <c r="H93" t="n">
+        <v>756</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>453</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>抖音示范店铺46</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>2.878521795501206</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>REF0097</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>白牌 中老年牛仔裤 宽松直筒 高腰 舒适</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>工厂直供</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>49</v>
+      </c>
+      <c r="G94" t="n">
+        <v>71</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3685</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>1571</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>抖音示范店铺37</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>3.56643749219507</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>REF0098</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>自主品牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>49</v>
+      </c>
+      <c r="G95" t="n">
+        <v>64</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4206</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>2190</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>抖音示范店铺93</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>3.623869268350302</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>REF0099</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>无品牌 锥形牛仔裤 九分 春夏薄款</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>94</v>
+      </c>
+      <c r="G96" t="n">
+        <v>118</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1382</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>712</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>抖音示范店铺38</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>3.14050804303818</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>80-99</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>REF0100</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>自主品牌 锥形牛仔裤 九分 春夏薄款</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>自主品牌</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>49</v>
+      </c>
+      <c r="G97" t="n">
+        <v>73</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2268</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>636</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>抖音示范店铺62</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>3.355643050220869</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>REF0101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>工厂直供 中老年牛仔裤 宽松直筒 高腰 舒适</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>自主品牌</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>114</v>
+      </c>
+      <c r="G98" t="n">
+        <v>150</v>
+      </c>
+      <c r="H98" t="n">
+        <v>792</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>397</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>抖音示范店铺12</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>2.898725181589493</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>REF0102</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>工厂直供 加绒牛仔裤 秋冬 保暖 直筒</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>自主品牌</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>84</v>
+      </c>
+      <c r="G99" t="n">
+        <v>122</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1587</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>745</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>抖音示范店铺14</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>3.200576926754848</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>80-99</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>REF0103</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>自主品牌 阔腿牛仔裤 复古 水洗 做旧</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>74</v>
+      </c>
+      <c r="G100" t="n">
+        <v>107</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>551</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>抖音示范店铺15</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>3.079181246047625</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>60-79</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>REF0104</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>工厂直供 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>59</v>
+      </c>
+      <c r="G101" t="n">
+        <v>89</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1707</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>408</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>抖音示范店铺86</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>3.232233521114733</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>REF0105</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>抖音</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>白牌 中老年牛仔裤 宽松直筒 高腰 舒适</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>工厂直供</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>133</v>
+      </c>
+      <c r="G102" t="n">
+        <v>202</v>
+      </c>
+      <c r="H102" t="n">
+        <v>613</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>301</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>抖音示范店铺36</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2.787460474518415</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>120-139</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>REF0106</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>白牌 锥形牛仔裤 九分 春夏薄款</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>自主品牌</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>102</v>
+      </c>
+      <c r="G103" t="n">
+        <v>157</v>
+      </c>
+      <c r="H103" t="n">
+        <v>581</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>219</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺70</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>2.764176132390331</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>REF0107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>白牌 阔腿牛仔裤 复古 水洗 做旧</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>160</v>
+      </c>
+      <c r="G104" t="n">
+        <v>246</v>
+      </c>
+      <c r="H104" t="n">
+        <v>237</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>139</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺83</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>2.374748346010104</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>140-159</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>REF0108</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>白牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>无品牌</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>90</v>
+      </c>
+      <c r="G105" t="n">
+        <v>134</v>
+      </c>
+      <c r="H105" t="n">
+        <v>766</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>456</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺76</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>2.884228769632604</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>80-99</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>REF0109</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>无品牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>134</v>
+      </c>
+      <c r="G106" t="n">
+        <v>168</v>
+      </c>
+      <c r="H106" t="n">
+        <v>550</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>308</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺23</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>2.740362689494244</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>120-139</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>REF0111</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>工厂直供 牛仔裤 男 直筒 宽松 大码 百搭</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>117</v>
+      </c>
+      <c r="G107" t="n">
+        <v>164</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1398</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>715</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺79</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>3.145507171409663</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>100-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>REF0112</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>工厂直供 牛仔裤 男 直筒 宽松 大码 百搭</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>工厂直供</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>76</v>
+      </c>
+      <c r="G108" t="n">
+        <v>117</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3818</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>1463</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺88</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>3.581835924057648</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>60-79</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>REF0113</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>自主品牌 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>162</v>
+      </c>
+      <c r="G109" t="n">
+        <v>210</v>
+      </c>
+      <c r="H109" t="n">
+        <v>239</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>79</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺75</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2.378397900948137</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>160-179</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>REF0114</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>工厂直供 阔腿牛仔裤 复古 水洗 做旧</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>154</v>
+      </c>
+      <c r="G110" t="n">
+        <v>217</v>
+      </c>
+      <c r="H110" t="n">
+        <v>500</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>299</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺90</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>2.698970004336019</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>140-159</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>REF0115</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>工厂直供 牛仔裤 女 高腰 小脚 显瘦 弹力</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>157</v>
+      </c>
+      <c r="G111" t="n">
+        <v>217</v>
+      </c>
+      <c r="H111" t="n">
+        <v>981</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>536</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺59</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>2.991669007379949</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>140-159</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>REF0116</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>自主品牌 锥形牛仔裤 九分 春夏薄款</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>工厂直供</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>153</v>
+      </c>
+      <c r="G112" t="n">
+        <v>206</v>
+      </c>
+      <c r="H112" t="n">
+        <v>334</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>109</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺9</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>2.523746466811565</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>140-159</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>REF0117</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>自主品牌 牛仔裤 男 直筒 宽松 大码 百搭</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>131</v>
+      </c>
+      <c r="G113" t="n">
+        <v>169</v>
+      </c>
+      <c r="H113" t="n">
+        <v>546</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>191</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺53</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>2.737192642704737</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>120-139</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>REF0118</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>白牌 中老年牛仔裤 宽松直筒 高腰 舒适</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>自主品牌</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>127</v>
+      </c>
+      <c r="G114" t="n">
+        <v>192</v>
+      </c>
+      <c r="H114" t="n">
+        <v>498</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>249</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺46</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>2.697229342759718</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>120-139</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>REF0119</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>自主品牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>152</v>
+      </c>
+      <c r="G115" t="n">
+        <v>206</v>
+      </c>
+      <c r="H115" t="n">
+        <v>258</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>139</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺36</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>2.41161970596323</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>140-159</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>REF0120</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>微信视频号</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>白牌 加绒牛仔裤 秋冬 保暖 直筒</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>白牌</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>144</v>
+      </c>
+      <c r="G116" t="n">
+        <v>222</v>
+      </c>
+      <c r="H116" t="n">
+        <v>802</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>近30天</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>432</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>微信视频号示范店铺85</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:14:43</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>2.904174368284163</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>140-159</t>
         </is>
       </c>
     </row>
@@ -7822,10 +9691,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
         <v>22</v>
@@ -7972,16 +9841,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46872.29</v>
+        <v>59802.57</v>
       </c>
       <c r="D4" t="n">
-        <v>42493.29</v>
+        <v>53389</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.34</v>
+        <v>-10.72</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -7999,13 +9868,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29093.14</v>
+        <v>42023.43</v>
       </c>
       <c r="D5" t="n">
-        <v>18522.71</v>
+        <v>29418.43</v>
       </c>
       <c r="E5" t="n">
-        <v>-36.33</v>
+        <v>-30</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
